--- a/资料/素材补充描述_102941.xlsx
+++ b/资料/素材补充描述_102941.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>编号</t>
   </si>
@@ -181,6 +181,162 @@
     <t>成分跟产生过程都成谜的结晶。/有时会在刮着强烈暴风雨后的隔天等日子被冲到岸上来。/其带着泪水颜色和形状的外观，会让人联想到很悲伤的故事。</t>
   </si>
   <si>
+    <t>药木的树根</t>
+  </si>
+  <si>
+    <t>也能用作草药的树根。/由于不挖得很深就无法采集到，因此很辛苦。/在采集到后，要用水清洗干净再使用。/对了对了，挖完土之后记得把土再埋回去哦。</t>
+  </si>
+  <si>
+    <t>强韧藤蔓</t>
+  </si>
+  <si>
+    <t>纠缠草</t>
+  </si>
+  <si>
+    <t>又长又弯曲的藤蔓。/非常强韧，具有会缠绕住附近物体的性质，相当棘手。/有时候会在森林里被它给绊倒，一旦缠住就很难解开。</t>
+  </si>
+  <si>
+    <t>清新薄荷</t>
+  </si>
+  <si>
+    <t>新鲜的薄荷叶片。/是会散发清新香味的代表性香草。/可在想给茶或蛋糕添加一点风味时使用。/也能将叶片切碎使用，或是磨碎当成药。</t>
+  </si>
+  <si>
+    <t>贤者的香草</t>
+  </si>
+  <si>
+    <t>在香草当中，也是含有特别多药用成分的草。/外表很不起眼，但只要在调合上下工夫，就能成为各种药。/只不过，不知是否是外表很不起眼所致，直到最近才被拿来使用。</t>
+  </si>
+  <si>
+    <t>小麦</t>
+  </si>
+  <si>
+    <t>面粉的原料。/将小麦磨碎，就能变成纯白的面粉。/起初是青翠的绿色，但是到收获前将会转为金黄色，/让小麦田变得就像是铺上了金色的绒毯一样。</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>红萝卜</t>
+  </si>
+  <si>
+    <t>蔬菜之王的红萝卜。/虽然味道有些独特，但营养满分，很适合作为各种料理呢。/要煮要烤都任君挑选，连生吃也……这可能得看人吧。</t>
+  </si>
+  <si>
+    <t>五谷麦</t>
+  </si>
+  <si>
+    <t>五种类的小麦合为一根麦穗的神奇小麦。/营养价值极高。/但如果水量调整得不好，就不管做什么都会做出很硬的东西来。</t>
+  </si>
+  <si>
+    <t>独角兽的角</t>
+  </si>
+  <si>
+    <t>神话中也提到过的独角兽的角。/含有万灵药的成分，是非常贵重的物品。/那螺旋状的构造，感觉好像能创造出神奇的力量。/此外，熬煮之后也会变成药。</t>
+  </si>
+  <si>
+    <t>巨兽的心脏</t>
+  </si>
+  <si>
+    <t>正如其名，是积蓄非常强大生命力的巨兽的心脏。/即使离开本体，也还是会发出噼噼啪啪的声音跳动着哦。/生命力到底是有多强啊……？</t>
+  </si>
+  <si>
+    <t>药泉的泉水</t>
+  </si>
+  <si>
+    <t>从称为药泉的泉水中涌出的液体。/有着漂亮的绿色，看上去就很有药的感觉。/但臭味相当刺鼻。只要调合得好也能成为香料。/当然，作为药用材料是无可挑剔的。</t>
+  </si>
+  <si>
+    <t>臭气石</t>
+  </si>
+  <si>
+    <t>虽然颜色很漂亮却超级臭。/是什么呢？就像蛋腐坏一样的味道吧？/虽然我没让蛋腐坏过，但大概就是那种印象。/近似硫磺的成分，能在调合时派上用场。</t>
+  </si>
+  <si>
+    <t>黑之魔石</t>
+  </si>
+  <si>
+    <t>注入了负面能量的黑暗之石。/其来由则不得而知。光是靠近它，便可能会感到不太舒服。/不过只要用炼金术，就有机会将负面能量转变为别种力量哦。</t>
+  </si>
+  <si>
+    <t>肥料</t>
+  </si>
+  <si>
+    <t>用植物或动物的排泄物制作而成的天然肥料。/只要不在意臭味，对植物来说是最棒的肥料。/可以根据想栽培的植物，改变混合的配方。</t>
+  </si>
+  <si>
+    <t>熏木的树皮</t>
+  </si>
+  <si>
+    <t>将带有香气的树木的树皮剥下后所制成的。/香味会因使用的树木而不同。用于熏制物品或辛香料。/也能将其弄得细细碎碎，以碎片状装入布袋，当作香包使用。</t>
+  </si>
+  <si>
+    <t>龙肉</t>
+  </si>
+  <si>
+    <t>地上最强的生物——龙的肉。/由于鳞片实在太硬，因此去掉会比较好。/将它烤得金黄，会意外有嚼劲而且很好吃。仔细烤熟这点很重要。</t>
+  </si>
+  <si>
+    <t>岩盐</t>
+  </si>
+  <si>
+    <t>盐的结晶在凝固后，成有如岩石般的状态。/虽然外表看起来像漂亮的宝石一样，但只要舔舔看，就会吃到超咸的味道。/由于太硬，因此可能无法用在料理上。调合的话就能使用。</t>
+  </si>
+  <si>
+    <t>夏利欧鲜奶</t>
+  </si>
+  <si>
+    <t>动物的奶。/含有丰富的钙质，每天喝就会精力百倍。/奶酪等乳制品大多都是用这个奶作为原料。/因为很容易腐坏，必须要注意。</t>
+  </si>
+  <si>
+    <t>森林甘露</t>
+  </si>
+  <si>
+    <t>只能从巨大树木中采集到数滴的贵重液体。/收集必须要耗费相当大的毅力。/但相对的，采集到的液体里含有大量贵重的药用成分。</t>
+  </si>
+  <si>
+    <t>熔岩石</t>
+  </si>
+  <si>
+    <t>为岩浆在接触地表空气后，一口气冷却下来而成。/尽管其在外层勉强保有固体状态，但在内部则仍维持着火热岩浆的液体状。/使用上请务必小心。</t>
+  </si>
+  <si>
+    <t>蒸馏石</t>
+  </si>
+  <si>
+    <t>开有无数细小孔洞，像浮石一样的东西。/那无数的洞具有过滤的功用，可用于过滤水或酒精和其他液体哦。</t>
+  </si>
+  <si>
+    <t>幽明石</t>
+  </si>
+  <si>
+    <t>拥有蓄光效果的神奇石头。/由于其放出的光芒很淡，且看起来有些诡异，故有时会被误认为幽灵。/要是光芒变弱，只要拿去晒太阳，就又能回到发光状态。</t>
+  </si>
+  <si>
+    <t>黑阳矿</t>
+  </si>
+  <si>
+    <t>漆黑且尖锐的岩石块。/经研磨过后，就会犹如黑色的镜子般闪闪发亮。/而在冶炼过程中，它会因加热而绽放出像太阳一样的耀眼光芒。/听说这便是其名称的由来哦。</t>
+  </si>
+  <si>
+    <t>彩虹碎片</t>
+  </si>
+  <si>
+    <t>散发七彩光辉的神奇矿石。/虽然因散发七彩光芒而被称为彩虹碎片，/但其色彩跟高挂在空中的彩虹不同，看起来给人有毒的感觉。/具有神秘力量，却也有着毒。</t>
+  </si>
+  <si>
+    <t>软毛</t>
+  </si>
+  <si>
+    <t>似乎是某种动物的毛。/非常柔软，十分蓬松。只要一摸，就会不自觉想把脸埋进去。/能够进行许多不同的加工，成为各种道具的材料哦。</t>
+  </si>
+  <si>
+    <t>药虫的丝</t>
+  </si>
+  <si>
+    <t>体内含有药用成分的虫用来织巢而吐出的丝，将其加工而成的物品。/除了药的材料以外，也能作为火药的材料。/由于是很强韧的丝，因此也能用于衣服上。</t>
+  </si>
+  <si>
     <t>佐尼果</t>
   </si>
   <si>
@@ -190,88 +346,16 @@
     <t>月光花</t>
   </si>
   <si>
-    <t>臭气石</t>
-  </si>
-  <si>
-    <t>黑之魔石</t>
-  </si>
-  <si>
-    <t>肥料</t>
-  </si>
-  <si>
     <t>芬芳虫</t>
   </si>
   <si>
     <t>美丽贝壳</t>
   </si>
   <si>
-    <t>药木的树根</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>强韧藤蔓</t>
-  </si>
-  <si>
-    <t>清新薄荷</t>
-  </si>
-  <si>
-    <t>贤者的香草</t>
-  </si>
-  <si>
-    <t>小麦</t>
-  </si>
-  <si>
-    <t>萝卜</t>
-  </si>
-  <si>
-    <t>五谷麦</t>
-  </si>
-  <si>
-    <t>独角兽的角</t>
-  </si>
-  <si>
-    <t>巨兽的心脏</t>
-  </si>
-  <si>
-    <t>药泉的泉水</t>
-  </si>
-  <si>
-    <t>熏木的树皮</t>
-  </si>
-  <si>
-    <t>龙肉</t>
-  </si>
-  <si>
-    <t>岩盐</t>
-  </si>
-  <si>
-    <t>夏利欧鲜奶</t>
-  </si>
-  <si>
-    <t>森林甘露</t>
-  </si>
-  <si>
-    <t>熔岩石</t>
-  </si>
-  <si>
-    <t>蒸馏石</t>
-  </si>
-  <si>
-    <t>幽明石</t>
-  </si>
-  <si>
-    <t>黑阳矿</t>
-  </si>
-  <si>
-    <t>彩虹碎片</t>
-  </si>
-  <si>
-    <t>软毛</t>
-  </si>
-  <si>
-    <t>药虫的丝</t>
+    <t>不要给表格排序</t>
+  </si>
+  <si>
+    <t>添加描述时，也看一下c列游戏原名对应的物品，将那些物品的名字全部替换</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1294,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1500,23 +1584,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>31</v>
-      </c>
-      <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" t="s">
-        <v>56</v>
-      </c>
-    </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
         <v>56</v>
@@ -1524,299 +1597,326 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
         <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>104</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>262</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
         <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
         <v>85</v>
       </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>184</v>
+        <v>289</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>203</v>
+        <v>290</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>289</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>290</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52">
-        <v>291</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>362</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>366</v>
+        <v>88</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>122</v>
+      </c>
+      <c r="B55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>262</v>
+      </c>
+      <c r="B56" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
